--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132308635</v>
+        <v>132347494</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>80420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,48 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664852</v>
+        <v>664257</v>
       </c>
       <c r="R2" t="n">
-        <v>7047924</v>
+        <v>7047777</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +754,3697 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132348286</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97960</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>664249</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7047643</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Monika Norberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Monika Norberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132347797</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>664267</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7047725</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132350005</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79315</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>664012</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7047624</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132349689</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97960</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>664012</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7047624</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132348940</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79315</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>664235</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7047582</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132349043</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80420</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>664235</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7047582</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132350256</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79315</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>664359</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7047749</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132350023</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>664213</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7047624</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132346723</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80420</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>664313</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7047800</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132347422</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91889</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>664267</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7047725</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132349494</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79315</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>664237</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7047579</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132308635</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91884</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>664852</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7047924</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132340496</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>664852</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7047924</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132342341</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92183</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>658</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>664477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7047782</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132344149</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91884</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>664456</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7047718</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132339227</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>664661</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7047845</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132345129</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92261</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>664431</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7047720</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132338335</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79310</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>664712</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7047894</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132341333</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97955</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>664491</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7047881</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132344683</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79310</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>664460</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7047763</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132345459</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>664460</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7047763</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132341238</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99090</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>664852</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7047924</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132337954</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56517</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>664727</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7048010</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132341592</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80444</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>664852</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7047924</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132346045</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80420</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>664431</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7047720</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132342201</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91884</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>664417</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7047764</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132341405</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80415</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>664852</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7047924</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132344879</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91889</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>664431</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7047720</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Upp till 30 cm på grenuttag</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132338244</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91884</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>664730</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7047973</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132351388</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79315</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>664569</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7047936</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132338021</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79310</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>664730</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7047973</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132339055</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79310</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>664626</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7047837</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132343786</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97955</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>664477</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7047782</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132350984</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>664463</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7047834</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132351105</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>664525</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7047850</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132350901</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79315</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>664463</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7047834</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132348286</v>
+        <v>132347494</v>
       </c>
       <c r="B2" t="n">
-        <v>97960</v>
+        <v>80422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664249</v>
+        <v>664257</v>
       </c>
       <c r="R2" t="n">
-        <v>7047643</v>
+        <v>7047777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,57 +760,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132347494</v>
+        <v>132348286</v>
       </c>
       <c r="B3" t="n">
-        <v>80420</v>
+        <v>97963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664257</v>
+        <v>664249</v>
       </c>
       <c r="R3" t="n">
-        <v>7047777</v>
+        <v>7047643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -881,7 +881,7 @@
         <v>132347797</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>132349697</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>132349689</v>
       </c>
       <c r="B6" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132348940</v>
+        <v>132350256</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664235</v>
+        <v>664359</v>
       </c>
       <c r="R7" t="n">
-        <v>7047582</v>
+        <v>7047749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
         <v>132349043</v>
       </c>
       <c r="B8" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132350256</v>
+        <v>132348940</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664359</v>
+        <v>664235</v>
       </c>
       <c r="R9" t="n">
-        <v>7047749</v>
+        <v>7047582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1472,7 @@
         <v>132350023</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>132346723</v>
       </c>
       <c r="B11" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>132347422</v>
       </c>
       <c r="B12" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>132349494</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>132349071</v>
       </c>
       <c r="B14" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>132308635</v>
       </c>
       <c r="B15" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>132342341</v>
       </c>
       <c r="B17" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132339227</v>
+        <v>132344149</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,39 +2304,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>664661</v>
+        <v>664456</v>
       </c>
       <c r="R18" t="n">
-        <v>7047845</v>
+        <v>7047718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,11 +2373,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132344149</v>
+        <v>132339227</v>
       </c>
       <c r="B19" t="n">
-        <v>91889</v>
+        <v>57948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,43 +2410,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>664456</v>
+        <v>664661</v>
       </c>
       <c r="R19" t="n">
-        <v>7047718</v>
+        <v>7047845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,6 +2475,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,32 +2506,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132338335</v>
+        <v>132341333</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>97963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>664712</v>
+        <v>664491</v>
       </c>
       <c r="R20" t="n">
-        <v>7047894</v>
+        <v>7047881</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,45 +2603,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132341333</v>
+        <v>132345129</v>
       </c>
       <c r="B21" t="n">
-        <v>97960</v>
+        <v>92264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>664491</v>
+        <v>664431</v>
       </c>
       <c r="R21" t="n">
-        <v>7047881</v>
+        <v>7047720</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,61 +2692,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132345129</v>
+        <v>132338335</v>
       </c>
       <c r="B22" t="n">
-        <v>92261</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>664431</v>
+        <v>664712</v>
       </c>
       <c r="R22" t="n">
-        <v>7047720</v>
+        <v>7047894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,12 +2789,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2804,7 +2804,7 @@
         <v>132344683</v>
       </c>
       <c r="B23" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>132345459</v>
       </c>
       <c r="B24" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>132341238</v>
       </c>
       <c r="B25" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132341592</v>
       </c>
       <c r="B26" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>132346045</v>
       </c>
       <c r="B27" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>132342201</v>
       </c>
       <c r="B29" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>132344879</v>
       </c>
       <c r="B30" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>132341405</v>
       </c>
       <c r="B31" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>132338244</v>
       </c>
       <c r="B32" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>132351388</v>
       </c>
       <c r="B33" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132343786</v>
+        <v>132338021</v>
       </c>
       <c r="B34" t="n">
-        <v>97960</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3960,21 +3960,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>664477</v>
+        <v>664730</v>
       </c>
       <c r="R34" t="n">
-        <v>7047782</v>
+        <v>7047973</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,54 +4028,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132350984</v>
+        <v>132339055</v>
       </c>
       <c r="B35" t="n">
-        <v>99095</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>664463</v>
+        <v>664626</v>
       </c>
       <c r="R35" t="n">
-        <v>7047834</v>
+        <v>7047837</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4127,22 +4113,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132351105</v>
+        <v>132350984</v>
       </c>
       <c r="B36" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4169,7 +4155,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4183,13 +4169,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>664525</v>
+        <v>664463</v>
       </c>
       <c r="R36" t="n">
-        <v>7047850</v>
+        <v>7047834</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4245,37 +4231,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132338021</v>
+        <v>132351105</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>99098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4284,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>664730</v>
+        <v>664525</v>
       </c>
       <c r="R37" t="n">
-        <v>7047973</v>
+        <v>7047850</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,48 +4337,57 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132339055</v>
+        <v>132343786</v>
       </c>
       <c r="B38" t="n">
-        <v>79315</v>
+        <v>97963</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>664626</v>
+        <v>664477</v>
       </c>
       <c r="R38" t="n">
-        <v>7047837</v>
+        <v>7047782</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4431,12 +4431,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4446,7 +4446,7 @@
         <v>132350901</v>
       </c>
       <c r="B39" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>132346388</v>
       </c>
       <c r="B40" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>132390172</v>
       </c>
       <c r="B41" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>132340874</v>
       </c>
       <c r="B42" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -2506,45 +2506,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132341333</v>
+        <v>132345129</v>
       </c>
       <c r="B20" t="n">
-        <v>97963</v>
+        <v>92264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>664491</v>
+        <v>664431</v>
       </c>
       <c r="R20" t="n">
-        <v>7047881</v>
+        <v>7047720</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,61 +2595,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132345129</v>
+        <v>132338335</v>
       </c>
       <c r="B21" t="n">
-        <v>92264</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>664431</v>
+        <v>664712</v>
       </c>
       <c r="R21" t="n">
-        <v>7047720</v>
+        <v>7047894</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,44 +2692,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132338335</v>
+        <v>132341333</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>664712</v>
+        <v>664491</v>
       </c>
       <c r="R22" t="n">
-        <v>7047894</v>
+        <v>7047881</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -984,7 +984,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132349697</v>
+        <v>132350005</v>
       </c>
       <c r="B5" t="n">
         <v>79317</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132350256</v>
+        <v>132348940</v>
       </c>
       <c r="B7" t="n">
         <v>79317</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664359</v>
+        <v>664235</v>
       </c>
       <c r="R7" t="n">
-        <v>7047749</v>
+        <v>7047582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132348940</v>
+        <v>132350256</v>
       </c>
       <c r="B9" t="n">
         <v>79317</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>664235</v>
+        <v>664359</v>
       </c>
       <c r="R9" t="n">
-        <v>7047582</v>
+        <v>7047749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3927,37 +3927,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132338021</v>
+        <v>132350984</v>
       </c>
       <c r="B34" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3966,13 +3971,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>664730</v>
+        <v>664463</v>
       </c>
       <c r="R34" t="n">
-        <v>7047973</v>
+        <v>7047834</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4028,48 +4033,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132339055</v>
+        <v>132351105</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>664626</v>
+        <v>664525</v>
       </c>
       <c r="R35" t="n">
-        <v>7047837</v>
+        <v>7047850</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4113,54 +4127,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132350984</v>
+        <v>132338021</v>
       </c>
       <c r="B36" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4169,13 +4178,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>664463</v>
+        <v>664730</v>
       </c>
       <c r="R36" t="n">
-        <v>7047834</v>
+        <v>7047973</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4231,57 +4240,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132351105</v>
+        <v>132339055</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>664525</v>
+        <v>664626</v>
       </c>
       <c r="R37" t="n">
-        <v>7047850</v>
+        <v>7047837</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4325,12 +4325,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -3415,10 +3415,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132342201</v>
+        <v>132341405</v>
       </c>
       <c r="B29" t="n">
-        <v>91892</v>
+        <v>80422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,37 +3426,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>664417</v>
+        <v>664852</v>
       </c>
       <c r="R29" t="n">
-        <v>7047764</v>
+        <v>7047924</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3500,19 +3509,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132344879</v>
+        <v>132342201</v>
       </c>
       <c r="B30" t="n">
         <v>91892</v>
@@ -3540,26 +3549,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>664431</v>
+        <v>664417</v>
       </c>
       <c r="R30" t="n">
-        <v>7047720</v>
+        <v>7047764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,11 +3594,6 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Upp till 30 cm på grenuttag</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3611,22 +3606,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341405</v>
+        <v>132344879</v>
       </c>
       <c r="B31" t="n">
-        <v>80422</v>
+        <v>91892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,46 +3629,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>664852</v>
+        <v>664431</v>
       </c>
       <c r="R31" t="n">
-        <v>7047924</v>
+        <v>7047720</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3703,6 +3698,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Upp till 30 cm på grenuttag</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -3415,10 +3415,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341405</v>
+        <v>132342201</v>
       </c>
       <c r="B29" t="n">
-        <v>80422</v>
+        <v>91892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,46 +3426,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>664852</v>
+        <v>664417</v>
       </c>
       <c r="R29" t="n">
-        <v>7047924</v>
+        <v>7047764</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3509,19 +3500,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132342201</v>
+        <v>132344879</v>
       </c>
       <c r="B30" t="n">
         <v>91892</v>
@@ -3549,17 +3540,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>664417</v>
+        <v>664431</v>
       </c>
       <c r="R30" t="n">
-        <v>7047764</v>
+        <v>7047720</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,6 +3594,11 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Upp till 30 cm på grenuttag</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3606,22 +3611,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132344879</v>
+        <v>132341405</v>
       </c>
       <c r="B31" t="n">
-        <v>91892</v>
+        <v>80422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,46 +3634,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>664431</v>
+        <v>664852</v>
       </c>
       <c r="R31" t="n">
-        <v>7047720</v>
+        <v>7047924</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3698,11 +3703,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Upp till 30 cm på grenuttag</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132347494</v>
       </c>
       <c r="B2" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132348286</v>
       </c>
       <c r="B3" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>132347797</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>132350005</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>132349689</v>
       </c>
       <c r="B6" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>132348940</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>132349043</v>
       </c>
       <c r="B8" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>132350256</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>132350023</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>132346723</v>
       </c>
       <c r="B11" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>132347422</v>
       </c>
       <c r="B12" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>132349494</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>132349071</v>
       </c>
       <c r="B14" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>132308635</v>
       </c>
       <c r="B15" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>132340496</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>132342341</v>
       </c>
       <c r="B17" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132344149</v>
+        <v>132339227</v>
       </c>
       <c r="B18" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,43 +2304,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>664456</v>
+        <v>664661</v>
       </c>
       <c r="R18" t="n">
-        <v>7047718</v>
+        <v>7047845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,6 +2369,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132339227</v>
+        <v>132344149</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,39 +2411,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>664661</v>
+        <v>664456</v>
       </c>
       <c r="R19" t="n">
-        <v>7047845</v>
+        <v>7047718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,7 +2509,7 @@
         <v>132345129</v>
       </c>
       <c r="B20" t="n">
-        <v>92264</v>
+        <v>92270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>132338335</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>132341333</v>
       </c>
       <c r="B22" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>132344683</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>132345459</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>132341238</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,57 +3101,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132341592</v>
+        <v>132346045</v>
       </c>
       <c r="B26" t="n">
-        <v>80451</v>
+        <v>80424</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>664852</v>
+        <v>664431</v>
       </c>
       <c r="R26" t="n">
-        <v>7047924</v>
+        <v>7047720</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3181,6 +3176,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,52 +3207,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132346045</v>
+        <v>132341592</v>
       </c>
       <c r="B27" t="n">
-        <v>80422</v>
+        <v>80453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>664431</v>
+        <v>664852</v>
       </c>
       <c r="R27" t="n">
-        <v>7047720</v>
+        <v>7047924</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3282,11 +3287,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,7 +3316,7 @@
         <v>132337954</v>
       </c>
       <c r="B28" t="n">
-        <v>56517</v>
+        <v>56518</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>132341405</v>
       </c>
       <c r="B29" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>132342201</v>
       </c>
       <c r="B30" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>132344879</v>
       </c>
       <c r="B31" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>132338244</v>
       </c>
       <c r="B32" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>132351388</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3927,42 +3927,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132350984</v>
+        <v>132343786</v>
       </c>
       <c r="B34" t="n">
-        <v>99098</v>
+        <v>97971</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3971,13 +3971,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>664463</v>
+        <v>664477</v>
       </c>
       <c r="R34" t="n">
-        <v>7047834</v>
+        <v>7047782</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4033,42 +4033,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132351105</v>
+        <v>132338021</v>
       </c>
       <c r="B35" t="n">
-        <v>99098</v>
+        <v>79319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4077,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>664525</v>
+        <v>664730</v>
       </c>
       <c r="R35" t="n">
-        <v>7047850</v>
+        <v>7047973</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4139,10 +4134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132338021</v>
+        <v>132339055</v>
       </c>
       <c r="B36" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4167,24 +4162,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>664730</v>
+        <v>664626</v>
       </c>
       <c r="R36" t="n">
-        <v>7047973</v>
+        <v>7047837</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4228,57 +4219,66 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132339055</v>
+        <v>132350984</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>99106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>664626</v>
+        <v>664463</v>
       </c>
       <c r="R37" t="n">
-        <v>7047837</v>
+        <v>7047834</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4325,54 +4325,54 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132343786</v>
+        <v>132351105</v>
       </c>
       <c r="B38" t="n">
-        <v>97963</v>
+        <v>99106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>664477</v>
+        <v>664525</v>
       </c>
       <c r="R38" t="n">
-        <v>7047782</v>
+        <v>7047850</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4446,7 +4446,7 @@
         <v>132350901</v>
       </c>
       <c r="B39" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>132346388</v>
       </c>
       <c r="B40" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>132390172</v>
       </c>
       <c r="B41" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>132340874</v>
       </c>
       <c r="B42" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>132338155</v>
       </c>
       <c r="B43" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132347494</v>
+        <v>132348286</v>
       </c>
       <c r="B2" t="n">
-        <v>80424</v>
+        <v>97971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664257</v>
+        <v>664249</v>
       </c>
       <c r="R2" t="n">
-        <v>7047777</v>
+        <v>7047643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,66 +769,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132348286</v>
+        <v>132347494</v>
       </c>
       <c r="B3" t="n">
-        <v>97971</v>
+        <v>80424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664249</v>
+        <v>664257</v>
       </c>
       <c r="R3" t="n">
-        <v>7047643</v>
+        <v>7047777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132339227</v>
+        <v>132344149</v>
       </c>
       <c r="B18" t="n">
-        <v>57949</v>
+        <v>91898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,39 +2304,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>664661</v>
+        <v>664456</v>
       </c>
       <c r="R18" t="n">
-        <v>7047845</v>
+        <v>7047718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,11 +2373,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132344149</v>
+        <v>132339227</v>
       </c>
       <c r="B19" t="n">
-        <v>91898</v>
+        <v>57949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,43 +2410,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>664456</v>
+        <v>664661</v>
       </c>
       <c r="R19" t="n">
-        <v>7047718</v>
+        <v>7047845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,6 +2475,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132348286</v>
       </c>
       <c r="B2" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132347494</v>
       </c>
       <c r="B3" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>132347797</v>
       </c>
       <c r="B4" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132350005</v>
+        <v>132349697</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>132349689</v>
       </c>
       <c r="B6" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>132348940</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>132349043</v>
       </c>
       <c r="B8" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>132350256</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>132350023</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>132346723</v>
       </c>
       <c r="B11" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>132347422</v>
       </c>
       <c r="B12" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>132349494</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>132349071</v>
       </c>
       <c r="B14" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>132308635</v>
       </c>
       <c r="B15" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>132340496</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>132342341</v>
       </c>
       <c r="B17" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132344149</v>
+        <v>132339227</v>
       </c>
       <c r="B18" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,43 +2304,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>664456</v>
+        <v>664661</v>
       </c>
       <c r="R18" t="n">
-        <v>7047718</v>
+        <v>7047845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,6 +2369,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,10 +2400,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132339227</v>
+        <v>132344149</v>
       </c>
       <c r="B19" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,39 +2411,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>664661</v>
+        <v>664456</v>
       </c>
       <c r="R19" t="n">
-        <v>7047845</v>
+        <v>7047718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,7 +2509,7 @@
         <v>132345129</v>
       </c>
       <c r="B20" t="n">
-        <v>92270</v>
+        <v>92280</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,32 +2607,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132338335</v>
+        <v>132341333</v>
       </c>
       <c r="B21" t="n">
-        <v>79319</v>
+        <v>97981</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>664712</v>
+        <v>664491</v>
       </c>
       <c r="R21" t="n">
-        <v>7047894</v>
+        <v>7047881</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,32 +2704,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132341333</v>
+        <v>132338335</v>
       </c>
       <c r="B22" t="n">
-        <v>97971</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>664491</v>
+        <v>664712</v>
       </c>
       <c r="R22" t="n">
-        <v>7047881</v>
+        <v>7047894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,7 +2804,7 @@
         <v>132344683</v>
       </c>
       <c r="B23" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>132345459</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>132341238</v>
       </c>
       <c r="B25" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,52 +3101,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132346045</v>
+        <v>132341592</v>
       </c>
       <c r="B26" t="n">
-        <v>80424</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>664431</v>
+        <v>664852</v>
       </c>
       <c r="R26" t="n">
-        <v>7047720</v>
+        <v>7047924</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3176,11 +3181,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,57 +3207,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132341592</v>
+        <v>132346045</v>
       </c>
       <c r="B27" t="n">
-        <v>80453</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>664852</v>
+        <v>664431</v>
       </c>
       <c r="R27" t="n">
-        <v>7047924</v>
+        <v>7047720</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3287,6 +3282,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,7 +3316,7 @@
         <v>132337954</v>
       </c>
       <c r="B28" t="n">
-        <v>56518</v>
+        <v>56522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341405</v>
+        <v>132342201</v>
       </c>
       <c r="B29" t="n">
-        <v>80424</v>
+        <v>91908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,46 +3426,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>664852</v>
+        <v>664417</v>
       </c>
       <c r="R29" t="n">
-        <v>7047924</v>
+        <v>7047764</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3509,22 +3500,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132342201</v>
+        <v>132344879</v>
       </c>
       <c r="B30" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3549,17 +3540,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>664417</v>
+        <v>664431</v>
       </c>
       <c r="R30" t="n">
-        <v>7047764</v>
+        <v>7047720</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,6 +3594,11 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Upp till 30 cm på grenuttag</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3606,22 +3611,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132344879</v>
+        <v>132341405</v>
       </c>
       <c r="B31" t="n">
-        <v>91898</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,46 +3634,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>664431</v>
+        <v>664852</v>
       </c>
       <c r="R31" t="n">
-        <v>7047720</v>
+        <v>7047924</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3698,11 +3703,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Upp till 30 cm på grenuttag</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3732,7 +3732,7 @@
         <v>132338244</v>
       </c>
       <c r="B32" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>132351388</v>
       </c>
       <c r="B33" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132343786</v>
+        <v>132338021</v>
       </c>
       <c r="B34" t="n">
-        <v>97971</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3960,21 +3960,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>664477</v>
+        <v>664730</v>
       </c>
       <c r="R34" t="n">
-        <v>7047782</v>
+        <v>7047973</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,10 +4028,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132338021</v>
+        <v>132339055</v>
       </c>
       <c r="B35" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4061,24 +4056,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>664730</v>
+        <v>664626</v>
       </c>
       <c r="R35" t="n">
-        <v>7047973</v>
+        <v>7047837</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4122,60 +4113,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132339055</v>
+        <v>132343786</v>
       </c>
       <c r="B36" t="n">
-        <v>79319</v>
+        <v>97981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>664626</v>
+        <v>664477</v>
       </c>
       <c r="R36" t="n">
-        <v>7047837</v>
+        <v>7047782</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4219,12 +4219,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4234,7 +4234,7 @@
         <v>132350984</v>
       </c>
       <c r="B37" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>132351105</v>
       </c>
       <c r="B38" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>132350901</v>
       </c>
       <c r="B39" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>132346388</v>
       </c>
       <c r="B40" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>132390172</v>
       </c>
       <c r="B41" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>132340874</v>
       </c>
       <c r="B42" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>132338155</v>
       </c>
       <c r="B43" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132348286</v>
+        <v>132347494</v>
       </c>
       <c r="B2" t="n">
-        <v>97981</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664249</v>
+        <v>664257</v>
       </c>
       <c r="R2" t="n">
-        <v>7047643</v>
+        <v>7047777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,57 +760,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132347494</v>
+        <v>132348286</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>97982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664257</v>
+        <v>664249</v>
       </c>
       <c r="R3" t="n">
-        <v>7047777</v>
+        <v>7047643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -881,7 +881,7 @@
         <v>132347797</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>132349689</v>
       </c>
       <c r="B6" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>132350023</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>132347422</v>
       </c>
       <c r="B12" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>132308635</v>
       </c>
       <c r="B15" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>132342341</v>
       </c>
       <c r="B17" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>132344149</v>
       </c>
       <c r="B19" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,49 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132345129</v>
+        <v>132338335</v>
       </c>
       <c r="B20" t="n">
-        <v>92280</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>664431</v>
+        <v>664712</v>
       </c>
       <c r="R20" t="n">
-        <v>7047720</v>
+        <v>7047894</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,57 +2591,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132341333</v>
+        <v>132345129</v>
       </c>
       <c r="B21" t="n">
-        <v>97981</v>
+        <v>92281</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>664491</v>
+        <v>664431</v>
       </c>
       <c r="R21" t="n">
-        <v>7047881</v>
+        <v>7047720</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,44 +2692,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132338335</v>
+        <v>132341333</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>97982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>664712</v>
+        <v>664491</v>
       </c>
       <c r="R22" t="n">
-        <v>7047894</v>
+        <v>7047881</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
         <v>132345459</v>
       </c>
       <c r="B24" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>132341238</v>
       </c>
       <c r="B25" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132342201</v>
+        <v>132341405</v>
       </c>
       <c r="B29" t="n">
-        <v>91908</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,37 +3426,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>664417</v>
+        <v>664852</v>
       </c>
       <c r="R29" t="n">
-        <v>7047764</v>
+        <v>7047924</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3500,22 +3509,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132344879</v>
+        <v>132342201</v>
       </c>
       <c r="B30" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3540,26 +3549,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>664431</v>
+        <v>664417</v>
       </c>
       <c r="R30" t="n">
-        <v>7047720</v>
+        <v>7047764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,11 +3594,6 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Upp till 30 cm på grenuttag</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3611,22 +3606,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132341405</v>
+        <v>132344879</v>
       </c>
       <c r="B31" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,46 +3629,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>664852</v>
+        <v>664431</v>
       </c>
       <c r="R31" t="n">
-        <v>7047924</v>
+        <v>7047720</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3703,6 +3698,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Upp till 30 cm på grenuttag</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3732,7 +3732,7 @@
         <v>132338244</v>
       </c>
       <c r="B32" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132338021</v>
+        <v>132343786</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>97982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3960,16 +3960,21 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>664730</v>
+        <v>664477</v>
       </c>
       <c r="R34" t="n">
-        <v>7047973</v>
+        <v>7047782</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4028,7 +4033,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132339055</v>
+        <v>132338021</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4056,20 +4061,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>664626</v>
+        <v>664730</v>
       </c>
       <c r="R35" t="n">
-        <v>7047837</v>
+        <v>7047973</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4113,69 +4122,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132343786</v>
+        <v>132339055</v>
       </c>
       <c r="B36" t="n">
-        <v>97981</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>664477</v>
+        <v>664626</v>
       </c>
       <c r="R36" t="n">
-        <v>7047782</v>
+        <v>7047837</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4219,12 +4219,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4234,7 +4234,7 @@
         <v>132350984</v>
       </c>
       <c r="B37" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>132351105</v>
       </c>
       <c r="B38" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>132346388</v>
       </c>
       <c r="B40" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>132348286</v>
       </c>
       <c r="B3" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>132347797</v>
       </c>
       <c r="B4" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>132349689</v>
       </c>
       <c r="B6" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>132350023</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132339227</v>
+        <v>132344149</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2304,39 +2304,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>664661</v>
+        <v>664456</v>
       </c>
       <c r="R18" t="n">
-        <v>7047845</v>
+        <v>7047718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,11 +2373,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2400,10 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132344149</v>
+        <v>132339227</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2411,43 +2410,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>664456</v>
+        <v>664661</v>
       </c>
       <c r="R19" t="n">
-        <v>7047718</v>
+        <v>7047845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,6 +2475,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,45 +2506,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132338335</v>
+        <v>132345129</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>92281</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>664712</v>
+        <v>664431</v>
       </c>
       <c r="R20" t="n">
-        <v>7047894</v>
+        <v>7047720</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,61 +2595,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132345129</v>
+        <v>132338335</v>
       </c>
       <c r="B21" t="n">
-        <v>92281</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>664431</v>
+        <v>664712</v>
       </c>
       <c r="R21" t="n">
-        <v>7047720</v>
+        <v>7047894</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,12 +2692,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
         <v>132341333</v>
       </c>
       <c r="B22" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>132345459</v>
       </c>
       <c r="B24" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>132341238</v>
       </c>
       <c r="B25" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132341405</v>
+        <v>132342201</v>
       </c>
       <c r="B29" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,46 +3426,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
+          <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>664852</v>
+        <v>664417</v>
       </c>
       <c r="R29" t="n">
-        <v>7047924</v>
+        <v>7047764</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3509,19 +3500,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132342201</v>
+        <v>132344879</v>
       </c>
       <c r="B30" t="n">
         <v>91909</v>
@@ -3549,17 +3540,26 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>664417</v>
+        <v>664431</v>
       </c>
       <c r="R30" t="n">
-        <v>7047764</v>
+        <v>7047720</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,6 +3594,11 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Upp till 30 cm på grenuttag</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3606,22 +3611,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132344879</v>
+        <v>132341405</v>
       </c>
       <c r="B31" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,46 +3634,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hädanbergsån, Hädanbergsån, Ång</t>
+          <t>Hädanbergsån, Utterån, Hundsjö, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>664431</v>
+        <v>664852</v>
       </c>
       <c r="R31" t="n">
-        <v>7047720</v>
+        <v>7047924</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3698,11 +3703,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Upp till 30 cm på grenuttag</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,32 +3927,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132343786</v>
+        <v>132338021</v>
       </c>
       <c r="B34" t="n">
-        <v>97982</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3960,21 +3960,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>664477</v>
+        <v>664730</v>
       </c>
       <c r="R34" t="n">
-        <v>7047782</v>
+        <v>7047973</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,7 +4028,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132338021</v>
+        <v>132339055</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4061,24 +4056,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>664730</v>
+        <v>664626</v>
       </c>
       <c r="R35" t="n">
-        <v>7047973</v>
+        <v>7047837</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4122,57 +4113,66 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132339055</v>
+        <v>132350984</v>
       </c>
       <c r="B36" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hädanbergsån, Hädanbergsån, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>664626</v>
+        <v>664463</v>
       </c>
       <c r="R36" t="n">
-        <v>7047837</v>
+        <v>7047834</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4219,22 +4219,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132350984</v>
+        <v>132351105</v>
       </c>
       <c r="B37" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>664463</v>
+        <v>664525</v>
       </c>
       <c r="R37" t="n">
-        <v>7047834</v>
+        <v>7047850</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4337,42 +4337,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132351105</v>
+        <v>132343786</v>
       </c>
       <c r="B38" t="n">
-        <v>99117</v>
+        <v>97983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>664525</v>
+        <v>664477</v>
       </c>
       <c r="R38" t="n">
-        <v>7047850</v>
+        <v>7047782</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 11228-2026 artfynd.xlsx
+++ b/artfynd/A 11228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132342341</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132308635</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132338244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132342201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344149</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346388</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132347422</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132345129</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132337974</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132338021</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132338335</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132339055</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344683</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132348940</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349494</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2390,6 +2475,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349697</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2487,6 +2577,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132350256</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2593,6 +2688,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132350901</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2690,6 +2790,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132351388</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2795,6 +2900,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132390172</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2896,6 +3006,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340874</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2993,6 +3108,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341177</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3099,6 +3219,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341405</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3205,6 +3330,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346045</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,6 +3432,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346723</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132347494</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3496,6 +3636,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349043</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3602,6 +3747,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341592</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3707,6 +3857,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132338155</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3809,6 +3964,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340496</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3916,6 +4076,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132339227</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4018,6 +4183,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132337954</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4115,6 +4285,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132342221</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4221,6 +4396,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341238</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4318,6 +4498,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132345459</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4424,6 +4609,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132347797</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4530,6 +4720,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132350023</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4636,6 +4831,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132350984</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4742,6 +4942,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132351105</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4839,6 +5044,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341333</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4945,6 +5155,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132343786</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5051,6 +5266,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132348286</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5148,6 +5368,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349689</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5249,8 +5474,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132349071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>